--- a/etf_holdings/2026-09-02_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-02_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,16 +451,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,28 +469,28 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00985A(633,000)</t>
+          <t>00981A(4,314,561)、00991A(1,150,020)、00982A(881,225)、00403A(1,387,956)、00985A(3,000)、00992A(152,675)、00405A(99,139)、00400A(438,197)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00993A(-97,000)</t>
+          <t>00993A(-8,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>致茂電子</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -499,58 +499,58 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00985A(38,000)</t>
+          <t>00985A(5,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00993A(-11,000)</t>
+          <t>00981A(-7,000)、00982A(-2,000)、00993A(-8,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00985A(5,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00993A(-8,000)</t>
+          <t>00981A(-1,868,000)、00982A(-8,000)、00403A(-1,500,000)、00993A(-100,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -559,88 +559,88 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00985A(167,000)</t>
+          <t>00403A(新納入)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00993A(-30,000)</t>
+          <t>00982A(-15,000)、00993A(-88,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(633,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00407A(-430,000)、00993A(-15,000)</t>
+          <t>00982A(-38,000)、00993A(-97,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00993A(新納入)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00985A(-448,000)</t>
+          <t>00991A(-150,000)、00982A(-6,000)、00993A(-11,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>欣興電子</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -649,162 +649,852 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00985A(50,000)</t>
+          <t>00985A(38,000)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00993A(-109,000)</t>
+          <t>00982A(-7,000)、00993A(-11,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00985A(10,000)、00993A(2,000)</t>
+          <t>00985A(167,000)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00982A(-7,000)、00993A(-30,000)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(新納入)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>00407A(全數賣出)、00993A(-5,000)</t>
+          <t>00982A(-1,000)、00992A(-50,000)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>緯穎科技服務</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>00985A(3,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>00993A(-8,000)</t>
+          <t>00982A(-2,000)、00405A(-100,000)、00993A(-24,000)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>鴻勁精密</t>
+          <t>信驊科技</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00991A(20,000)、00403A(40,000)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>00985A(-13,000)、00993A(-13,000)</t>
+          <t>00993A(-5,000)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>00991A(-200,000)、00982A(-3,000)、00993A(-57,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>00991A(-20,000)、00985A(-13,000)、00993A(-13,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>8299</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>群聯電子</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>全部減碼</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>00985A(-11,000)、00993A(-5,000)</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>00991A(-100,000)、00985A(-11,000)、00993A(-5,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>00403A(1,500,000)、00993A(新納入)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>00982A(-1,000)、00993A(-2,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>00403A(-300,000)、00993A(-15,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>00993A(106,000)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>00403A(-1,000,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>00403A(-2,000,000)、00993A(-114,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>00407A(-430,000)、00993A(-15,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>文曄科技</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>00993A(新納入)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>00985A(-448,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>欣興電子</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>00985A(50,000)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>00993A(-109,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>00993A(351,000)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>00982A(-1,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>00993A(172,000)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>00981A(-888,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>00405A(-60,000)、00993A(-7,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>貿聯控股（BizLink Holding In</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>00985A(10,000)、00993A(2,000)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>00993A(新納入)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>00982A(-20,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>00993A(54,000)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>00982A(-29,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>00981A(-7,000)、00993A(-19,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>00982A(-2,000)、00993A(-40,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>00985A(164,000)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>00982A(-8,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>00981A(84,000)、00407A(新納入)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>00407A(全數賣出)、00993A(-5,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>00993A(新納入)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>00403A(-200,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>金居</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>00993A(21,000)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>00403A(-200,000)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-09-02_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-02_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00993A(-8,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00981A(-7,000)、00982A(-2,000)、00993A(-8,000)</t>
+          <t>00981A(-7,000)、00982A(-2,000)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00981A(-1,868,000)、00982A(-8,000)、00403A(-1,500,000)、00993A(-100,000)</t>
+          <t>00981A(-1,868,000)、00982A(-8,000)、00403A(-1,500,000)</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -564,7 +564,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00982A(-15,000)、00993A(-88,000)</t>
+          <t>00982A(-15,000)</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00982A(-38,000)、00993A(-97,000)</t>
+          <t>00982A(-38,000)</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00991A(-150,000)、00982A(-6,000)、00993A(-11,000)</t>
+          <t>00991A(-150,000)、00982A(-6,000)</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00982A(-7,000)、00993A(-11,000)</t>
+          <t>00982A(-7,000)</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>00982A(-7,000)、00993A(-30,000)</t>
+          <t>00982A(-7,000)</t>
         </is>
       </c>
     </row>
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>00993A(新納入)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>00982A(-2,000)、00405A(-100,000)、00993A(-24,000)</t>
+          <t>00982A(-2,000)、00405A(-100,000)</t>
         </is>
       </c>
     </row>
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>00993A(-5,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -804,79 +804,79 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>00991A(-200,000)、00982A(-3,000)、00993A(-57,000)</t>
+          <t>00991A(-200,000)、00982A(-3,000)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>鴻勁精密</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00985A(164,000)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>00991A(-20,000)、00985A(-13,000)、00993A(-13,000)</t>
+          <t>00982A(-8,000)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>群聯電子</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>00981A(84,000)、00407A(新納入)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>00991A(-100,000)、00985A(-11,000)、00993A(-5,000)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>鴻勁精密</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -884,29 +884,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>00403A(1,500,000)、00993A(新納入)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00991A(-20,000)、00985A(-13,000)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>群聯電子</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -924,577 +924,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>00982A(-1,000)、00993A(-2,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>00403A(-300,000)、00993A(-15,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>00993A(106,000)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>00403A(-1,000,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>00403A(-2,000,000)、00993A(-114,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>00407A(-430,000)、00993A(-15,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>文曄科技</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>00993A(新納入)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>00985A(-448,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>欣興電子</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>00985A(50,000)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>00993A(-109,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>00993A(351,000)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>00982A(-1,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>00993A(172,000)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>00981A(-888,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>00405A(-60,000)、00993A(-7,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>貿聯控股（BizLink Holding In</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>00985A(10,000)、00993A(2,000)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>00993A(新納入)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>00982A(-20,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>亞翔</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>2</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>00993A(54,000)</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>00982A(-29,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>00981A(-7,000)、00993A(-19,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>6196</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>帆宣</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>00982A(-2,000)、00993A(-40,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>環球晶</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>00985A(164,000)</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>00982A(-8,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>00981A(84,000)、00407A(新納入)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>00407A(全數賣出)、00993A(-5,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>00993A(新納入)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>00403A(-200,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>金居</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>00993A(21,000)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>00403A(-200,000)</t>
+          <t>00991A(-100,000)、00985A(-11,000)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-09-02_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-02_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,7 +469,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00981A(4,314,561)、00991A(1,150,020)、00982A(881,225)、00403A(1,387,956)、00985A(3,000)、00992A(152,675)、00405A(99,139)、00400A(438,197)</t>
+          <t>00981A(4,314,561)、00991A(1,150,020)、00403A(1,387,956)、00992A(152,675)、00405A(99,139)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -481,450 +481,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00985A(5,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00981A(-7,000)、00982A(-2,000)</t>
+          <t>00981A(-1,868,000)、00403A(-1,500,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>信驊科技</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>00991A(20,000)、00403A(40,000)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>00981A(-1,868,000)、00982A(-8,000)、00403A(-1,500,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>光寶科</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>00403A(新納入)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>00982A(-15,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>00985A(633,000)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>00982A(-38,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>智邦科技</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>00991A(-150,000)、00982A(-6,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>00985A(38,000)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>00982A(-7,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>00985A(167,000)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>00982A(-7,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>00982A(-1,000)、00992A(-50,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>00982A(-2,000)、00405A(-100,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>信驊科技</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>00991A(20,000)、00403A(40,000)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>台燿科技</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>00991A(-200,000)、00982A(-3,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>環球晶</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>00985A(164,000)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>00982A(-8,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>00981A(84,000)、00407A(新納入)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>鴻勁精密</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>00991A(-20,000)、00985A(-13,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>00991A(-100,000)、00985A(-11,000)</t>
         </is>
       </c>
     </row>
